--- a/experiment1/data_processing3/exp_data/12_anova_effect_size.xlsx
+++ b/experiment1/data_processing3/exp_data/12_anova_effect_size.xlsx
@@ -476,28 +476,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9275.820501786766</v>
+        <v>7974.647850849351</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>9275.820501786766</v>
+        <v>7974.647850849351</v>
       </c>
       <c r="F2" t="n">
-        <v>17.02094232290799</v>
+        <v>14.2455344850609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001877434629323181</v>
+        <v>0.0005212259059175137</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001877434629323181</v>
+        <v>0.0005212259059175137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3038317746388178</v>
+        <v>0.2626121139793375</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -510,31 +510,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17987.73866472853</v>
+        <v>17732.24425326384</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>8993.869332364264</v>
+        <v>8866.122126631921</v>
       </c>
       <c r="F3" t="n">
-        <v>5.316490565444809</v>
+        <v>5.376748336781223</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00684653113873171</v>
+        <v>0.006442653802093497</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01434150189824535</v>
+        <v>0.01367286974485568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.119966416510207</v>
+        <v>0.1184912655458604</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7266842589878972</v>
+        <v>0.7269002011175631</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +544,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>980.1345820780334</v>
+        <v>1264.90302041754</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>490.0672910390167</v>
+        <v>632.4515102087698</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8341744495247305</v>
+        <v>1.088919478545535</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4380691355665919</v>
+        <v>0.3415158189406399</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4375836017001556</v>
+        <v>0.3411725020576515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02094117578818514</v>
+        <v>0.02650153599473725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9951258499844058</v>
+        <v>0.9922681992443019</v>
       </c>
     </row>
   </sheetData>
@@ -629,22 +629,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>15.77924334761667</v>
+        <v>15.03579820888246</v>
       </c>
       <c r="D2" t="n">
-        <v>28.15300933060933</v>
+        <v>27.55051705170763</v>
       </c>
       <c r="E2" t="n">
-        <v>3.544796802825392</v>
+        <v>3.494529113909218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001038897772051474</v>
+        <v>0.001175988052038914</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1966474511927807</v>
+        <v>0.1789506905589651</v>
       </c>
     </row>
     <row r="3">
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>6.747346694346395</v>
+        <v>4.994879270976536</v>
       </c>
       <c r="D3" t="n">
-        <v>33.28313729333063</v>
+        <v>34.52331207494139</v>
       </c>
       <c r="E3" t="n">
-        <v>1.282149788278411</v>
+        <v>0.9264126354277403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2073594745893866</v>
+        <v>0.3597876899350662</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08356911575980285</v>
+        <v>0.05891464183979547</v>
       </c>
     </row>
     <row r="4">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>14.77452355090454</v>
+        <v>14.13102090751138</v>
       </c>
       <c r="D4" t="n">
-        <v>39.23674616756176</v>
+        <v>38.62558219307437</v>
       </c>
       <c r="E4" t="n">
-        <v>2.381499503813742</v>
+        <v>2.342558411683439</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02221912093411223</v>
+        <v>0.02421440598248913</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1633677386047536</v>
+        <v>0.1500969070456722</v>
       </c>
     </row>
   </sheetData>
